--- a/data/equipment_maintenance.xlsx
+++ b/data/equipment_maintenance.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Equipment ID</t>
   </si>
@@ -45,18 +45,27 @@
     <t>BR4582</t>
   </si>
   <si>
+    <t>KK123</t>
+  </si>
+  <si>
     <t>2025-06-16</t>
   </si>
   <si>
     <t>2025-06-20</t>
   </si>
   <si>
+    <t>2023-06-06</t>
+  </si>
+  <si>
     <t xml:space="preserve">Full maintenance on suspension </t>
   </si>
   <si>
     <t xml:space="preserve">Suspension over hall </t>
   </si>
   <si>
+    <t xml:space="preserve">Maintenance </t>
+  </si>
+  <si>
     <t>BroNali</t>
   </si>
   <si>
@@ -70,6 +79,9 @@
   </si>
   <si>
     <t>The vehicle needs replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No major works </t>
   </si>
 </sst>
 </file>
@@ -437,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -477,19 +489,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -497,22 +509,45 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>5000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>250000</v>
       </c>
     </row>
   </sheetData>

--- a/data/equipment_maintenance.xlsx
+++ b/data/equipment_maintenance.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>Equipment ID</t>
   </si>
@@ -48,6 +43,9 @@
     <t>KK123</t>
   </si>
   <si>
+    <t>BU892</t>
+  </si>
+  <si>
     <t>2025-06-16</t>
   </si>
   <si>
@@ -57,6 +55,9 @@
     <t>2023-06-06</t>
   </si>
   <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Full maintenance on suspension </t>
   </si>
   <si>
@@ -66,6 +67,9 @@
     <t xml:space="preserve">Maintenance </t>
   </si>
   <si>
+    <t>Service</t>
+  </si>
+  <si>
     <t>BroNali</t>
   </si>
   <si>
@@ -82,13 +86,16 @@
   </si>
   <si>
     <t xml:space="preserve">No major works </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs over hall </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,14 +158,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -205,7 +204,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -237,10 +236,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -272,7 +270,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -448,20 +445,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,70 +472,93 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3">
         <v>5000000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G4">
         <v>250000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <v>1000000</v>
       </c>
     </row>
   </sheetData>
